--- a/3-19.xlsx
+++ b/3-19.xlsx
@@ -163,7 +163,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.67"/>
@@ -200,13 +200,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0</v>
@@ -229,13 +229,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <v>4</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0</v>
@@ -258,13 +258,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="0" t="n">
         <v>5</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>0</v>
@@ -285,129 +285,1053 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
